--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/70.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/70.xlsx
@@ -426,13 +426,13 @@
         <v>-7.09324999237949</v>
       </c>
       <c r="E2">
-        <v>-18.46818300351577</v>
+        <v>-23.45946253515881</v>
       </c>
       <c r="F2">
-        <v>-1.774851032444298</v>
+        <v>-3.968126031775771</v>
       </c>
       <c r="G2">
-        <v>-10.99817093279644</v>
+        <v>-13.48249543857425</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.883148224757031</v>
       </c>
       <c r="E3">
-        <v>-17.14169714490143</v>
+        <v>-24.35555110418117</v>
       </c>
       <c r="F3">
-        <v>-2.132680071064197</v>
+        <v>-3.881959254536567</v>
       </c>
       <c r="G3">
-        <v>-10.63762710476369</v>
+        <v>-13.30267518337214</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.77903314925299</v>
       </c>
       <c r="E4">
-        <v>-18.36631303614038</v>
+        <v>-24.36355018919279</v>
       </c>
       <c r="F4">
-        <v>-2.395779498602154</v>
+        <v>-3.698088198871966</v>
       </c>
       <c r="G4">
-        <v>-11.03734515538609</v>
+        <v>-13.08311809012099</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.943144106200772</v>
       </c>
       <c r="E5">
-        <v>-18.25629031493434</v>
+        <v>-24.60167871371316</v>
       </c>
       <c r="F5">
-        <v>-2.430543593395441</v>
+        <v>-4.085568648675074</v>
       </c>
       <c r="G5">
-        <v>-9.600799913965851</v>
+        <v>-13.21110592758343</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.351375934006408</v>
       </c>
       <c r="E6">
-        <v>-18.11579132902672</v>
+        <v>-24.51444050983513</v>
       </c>
       <c r="F6">
-        <v>-2.742979755076733</v>
+        <v>-3.883417181165494</v>
       </c>
       <c r="G6">
-        <v>-9.14941783862991</v>
+        <v>-12.94102570500506</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.019305568610574</v>
       </c>
       <c r="E7">
-        <v>-19.10122378006879</v>
+        <v>-25.21643290080295</v>
       </c>
       <c r="F7">
-        <v>-2.477234522054235</v>
+        <v>-3.808251123035467</v>
       </c>
       <c r="G7">
-        <v>-8.464727878281426</v>
+        <v>-12.86435596859783</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.906402247983949</v>
       </c>
       <c r="E8">
-        <v>-19.41784799862841</v>
+        <v>-26.28264946532426</v>
       </c>
       <c r="F8">
-        <v>-2.638715635188568</v>
+        <v>-3.668229695838058</v>
       </c>
       <c r="G8">
-        <v>-8.361713118205278</v>
+        <v>-12.45833558053248</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.988046623140906</v>
       </c>
       <c r="E9">
-        <v>-19.41102842563305</v>
+        <v>-25.76155019360935</v>
       </c>
       <c r="F9">
-        <v>-2.580688498622462</v>
+        <v>-3.599276393229027</v>
       </c>
       <c r="G9">
-        <v>-7.866555382937846</v>
+        <v>-12.39233726264144</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.201873495815778</v>
       </c>
       <c r="E10">
-        <v>-19.94653518743379</v>
+        <v>-26.71680956437654</v>
       </c>
       <c r="F10">
-        <v>-2.716000657134956</v>
+        <v>-3.57745802420669</v>
       </c>
       <c r="G10">
-        <v>-7.537705994241216</v>
+        <v>-12.0780323320619</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.499706982681698</v>
       </c>
       <c r="E11">
-        <v>-19.79754288436689</v>
+        <v>-28.00825893225462</v>
       </c>
       <c r="F11">
-        <v>-2.735045652092719</v>
+        <v>-3.464035474313174</v>
       </c>
       <c r="G11">
-        <v>-7.449828331304343</v>
+        <v>-12.12525678559825</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.824806605025344</v>
       </c>
       <c r="E12">
-        <v>-20.84945578908549</v>
+        <v>-27.95111905084763</v>
       </c>
       <c r="F12">
-        <v>-1.824900162554041</v>
+        <v>-3.272421668534606</v>
       </c>
       <c r="G12">
-        <v>-7.473614825273976</v>
+        <v>-11.81047147801395</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.128832566639745</v>
       </c>
       <c r="E13">
-        <v>-21.61799093189971</v>
+        <v>-28.52050771063633</v>
       </c>
       <c r="F13">
-        <v>-1.726084215074088</v>
+        <v>-3.204354719046571</v>
       </c>
       <c r="G13">
-        <v>-7.892886047511518</v>
+        <v>-11.56033342799479</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.384847141275988</v>
       </c>
       <c r="E14">
-        <v>-22.21721210863465</v>
+        <v>-28.25605820934486</v>
       </c>
       <c r="F14">
-        <v>-1.597580408245203</v>
+        <v>-2.91557010345001</v>
       </c>
       <c r="G14">
-        <v>-7.724647055315588</v>
+        <v>-11.50766557198597</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.569671201011596</v>
       </c>
       <c r="E15">
-        <v>-23.93669558886089</v>
+        <v>-29.79304750735247</v>
       </c>
       <c r="F15">
-        <v>-2.347457514527247</v>
+        <v>-3.048952165913981</v>
       </c>
       <c r="G15">
-        <v>-6.838196142221278</v>
+        <v>-11.10979723390637</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.687006085926154</v>
       </c>
       <c r="E16">
-        <v>-24.01917836577198</v>
+        <v>-29.82518920979532</v>
       </c>
       <c r="F16">
-        <v>-1.490754147980179</v>
+        <v>-2.730475549131475</v>
       </c>
       <c r="G16">
-        <v>-6.697064511114876</v>
+        <v>-10.74489607315106</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.74318158624891</v>
       </c>
       <c r="E17">
-        <v>-24.59369624154684</v>
+        <v>-30.68034995781715</v>
       </c>
       <c r="F17">
-        <v>-1.015274572242874</v>
+        <v>-2.552005448933127</v>
       </c>
       <c r="G17">
-        <v>-7.841607107625167</v>
+        <v>-10.62718673714383</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.758949450311284</v>
       </c>
       <c r="E18">
-        <v>-25.0148069506165</v>
+        <v>-31.31851372053934</v>
       </c>
       <c r="F18">
-        <v>-0.4946456595833849</v>
+        <v>-2.386619411861997</v>
       </c>
       <c r="G18">
-        <v>-6.253472897638818</v>
+        <v>-10.30157206099559</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.755501500376955</v>
       </c>
       <c r="E19">
-        <v>-25.54936262702386</v>
+        <v>-31.98563990243522</v>
       </c>
       <c r="F19">
-        <v>-0.7185550252948969</v>
+        <v>-2.063170933927888</v>
       </c>
       <c r="G19">
-        <v>-6.243264886287564</v>
+        <v>-10.31498998282162</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.748482340785555</v>
       </c>
       <c r="E20">
-        <v>-25.57178166175528</v>
+        <v>-32.5310894521476</v>
       </c>
       <c r="F20">
-        <v>-0.5009743865407732</v>
+        <v>-2.052710310365336</v>
       </c>
       <c r="G20">
-        <v>-6.216972077510462</v>
+        <v>-10.09291743715693</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.75690345644555</v>
       </c>
       <c r="E21">
-        <v>-27.24756089921035</v>
+        <v>-33.28436777316007</v>
       </c>
       <c r="F21">
-        <v>-0.02340235474399659</v>
+        <v>-2.082418878899337</v>
       </c>
       <c r="G21">
-        <v>-5.574394732788932</v>
+        <v>-10.03336635303364</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.78432407915144</v>
       </c>
       <c r="E22">
-        <v>-29.09804497104433</v>
+        <v>-33.03288875083604</v>
       </c>
       <c r="F22">
-        <v>0.01519790949165478</v>
+        <v>-1.630488960056219</v>
       </c>
       <c r="G22">
-        <v>-6.116163396613805</v>
+        <v>-9.474883702336456</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.838240968290824</v>
       </c>
       <c r="E23">
-        <v>-28.4070814327496</v>
+        <v>-33.6191082995186</v>
       </c>
       <c r="F23">
-        <v>-0.2971363629990932</v>
+        <v>-1.594753190299449</v>
       </c>
       <c r="G23">
-        <v>-6.691414859819707</v>
+        <v>-9.449456355391309</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.91553009427861</v>
       </c>
       <c r="E24">
-        <v>-27.69960887943866</v>
+        <v>-34.39781673347299</v>
       </c>
       <c r="F24">
-        <v>0.149511885283775</v>
+        <v>-1.249260199042039</v>
       </c>
       <c r="G24">
-        <v>-6.767069016580987</v>
+        <v>-9.652377784107884</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.00826506921921</v>
       </c>
       <c r="E25">
-        <v>-27.56960090533756</v>
+        <v>-34.47520767329985</v>
       </c>
       <c r="F25">
-        <v>0.3091324852314202</v>
+        <v>-1.375417241018793</v>
       </c>
       <c r="G25">
-        <v>-5.418193883902624</v>
+        <v>-9.747022497024924</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.113020853026634</v>
       </c>
       <c r="E26">
-        <v>-28.4769446770502</v>
+        <v>-34.28901920960778</v>
       </c>
       <c r="F26">
-        <v>0.7886727179772484</v>
+        <v>-1.355420451915213</v>
       </c>
       <c r="G26">
-        <v>-6.243003811828453</v>
+        <v>-9.403032095072131</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.214555452519306</v>
       </c>
       <c r="E27">
-        <v>-29.54779207219869</v>
+        <v>-33.98939200839501</v>
       </c>
       <c r="F27">
-        <v>0.8139312968234109</v>
+        <v>-1.445724095963998</v>
       </c>
       <c r="G27">
-        <v>-6.278564763904007</v>
+        <v>-9.515728801464423</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.309683934103623</v>
       </c>
       <c r="E28">
-        <v>-28.55225070479199</v>
+        <v>-34.649628012703</v>
       </c>
       <c r="F28">
-        <v>0.6275063844559794</v>
+        <v>-1.301871469528642</v>
       </c>
       <c r="G28">
-        <v>-6.560117903588028</v>
+        <v>-9.426920408080818</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.387567105321904</v>
       </c>
       <c r="E29">
-        <v>-28.13112338287702</v>
+        <v>-34.29761428044451</v>
       </c>
       <c r="F29">
-        <v>0.806369959170657</v>
+        <v>-1.227311776337464</v>
       </c>
       <c r="G29">
-        <v>-6.820505736871894</v>
+        <v>-9.324456515113395</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.44558079657619</v>
       </c>
       <c r="E30">
-        <v>-29.44405315972712</v>
+        <v>-34.2535258656258</v>
       </c>
       <c r="F30">
-        <v>0.7244328258901467</v>
+        <v>-1.139306851831447</v>
       </c>
       <c r="G30">
-        <v>-6.622347611661804</v>
+        <v>-9.427537849176616</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.484539512261848</v>
       </c>
       <c r="E31">
-        <v>-27.85152089006692</v>
+        <v>-34.03576261283673</v>
       </c>
       <c r="F31">
-        <v>0.771800530717028</v>
+        <v>-1.325701942972378</v>
       </c>
       <c r="G31">
-        <v>-7.253087840407228</v>
+        <v>-9.889618755846939</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.500613494093966</v>
       </c>
       <c r="E32">
-        <v>-29.38206855730972</v>
+        <v>-33.95372630614305</v>
       </c>
       <c r="F32">
-        <v>0.383456922080203</v>
+        <v>-1.582929902359291</v>
       </c>
       <c r="G32">
-        <v>-6.967730845853954</v>
+        <v>-9.912501932188048</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.501193060785201</v>
       </c>
       <c r="E33">
-        <v>-27.81497678361975</v>
+        <v>-33.60373311119409</v>
       </c>
       <c r="F33">
-        <v>-0.644540397854761</v>
+        <v>-1.458504148254389</v>
       </c>
       <c r="G33">
-        <v>-7.02916166608285</v>
+        <v>-9.331167434084852</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.483716806666525</v>
       </c>
       <c r="E34">
-        <v>-27.42652692840854</v>
+        <v>-33.03453549912633</v>
       </c>
       <c r="F34">
-        <v>0.2859348844834228</v>
+        <v>-1.459096430947391</v>
       </c>
       <c r="G34">
-        <v>-6.530256206954875</v>
+        <v>-9.512424904184369</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.453719258254573</v>
       </c>
       <c r="E35">
-        <v>-26.63765766294796</v>
+        <v>-32.48594612165238</v>
       </c>
       <c r="F35">
-        <v>0.04652096609371249</v>
+        <v>-1.525421323787339</v>
       </c>
       <c r="G35">
-        <v>-6.41784537709531</v>
+        <v>-9.810639815848877</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.411880685396638</v>
       </c>
       <c r="E36">
-        <v>-25.81106062581263</v>
+        <v>-32.29205760416409</v>
       </c>
       <c r="F36">
-        <v>-0.02316958350380992</v>
+        <v>-1.659716247129194</v>
       </c>
       <c r="G36">
-        <v>-7.085921864238244</v>
+        <v>-9.566481676315666</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.3538097610895</v>
       </c>
       <c r="E37">
-        <v>-25.57059799652771</v>
+        <v>-32.46199662854776</v>
       </c>
       <c r="F37">
-        <v>-0.2235019561968423</v>
+        <v>-1.688515268254922</v>
       </c>
       <c r="G37">
-        <v>-7.477525720671464</v>
+        <v>-9.32593289117967</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.281139900216536</v>
       </c>
       <c r="E38">
-        <v>-25.70753768032995</v>
+        <v>-31.72663733779627</v>
       </c>
       <c r="F38">
-        <v>0.01389405919964836</v>
+        <v>-1.599691088387537</v>
       </c>
       <c r="G38">
-        <v>-6.346545942312006</v>
+        <v>-9.968695598767169</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.184019926141531</v>
       </c>
       <c r="E39">
-        <v>-25.22068163598825</v>
+        <v>-31.64595705460015</v>
       </c>
       <c r="F39">
-        <v>0.1226984608225578</v>
+        <v>-1.626840001646888</v>
       </c>
       <c r="G39">
-        <v>-5.952331341287674</v>
+        <v>-9.616656271239977</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.061239959347212</v>
       </c>
       <c r="E40">
-        <v>-25.67836137077303</v>
+        <v>-30.80386646261755</v>
       </c>
       <c r="F40">
-        <v>0.05573323998024578</v>
+        <v>-1.542749113119099</v>
       </c>
       <c r="G40">
-        <v>-5.628630340924719</v>
+        <v>-9.923553214042229</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.906382216732853</v>
       </c>
       <c r="E41">
-        <v>-25.36904265093378</v>
+        <v>-30.19296022582021</v>
       </c>
       <c r="F41">
-        <v>-0.2624551049460863</v>
+        <v>-1.514102511595486</v>
       </c>
       <c r="G41">
-        <v>-5.894652161036207</v>
+        <v>-9.711516370585782</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.715625929636063</v>
       </c>
       <c r="E42">
-        <v>-23.91167664384012</v>
+        <v>-30.61823245263735</v>
       </c>
       <c r="F42">
-        <v>-0.3273957958559564</v>
+        <v>-1.646863298507357</v>
       </c>
       <c r="G42">
-        <v>-5.59934300810161</v>
+        <v>-9.676256959510502</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.492093137514523</v>
       </c>
       <c r="E43">
-        <v>-23.37668488024365</v>
+        <v>-29.22497126234242</v>
       </c>
       <c r="F43">
-        <v>-0.6089321966780216</v>
+        <v>-1.730480360880745</v>
       </c>
       <c r="G43">
-        <v>-5.500675137769666</v>
+        <v>-9.859754448469195</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.234463058802814</v>
       </c>
       <c r="E44">
-        <v>-23.28851635702887</v>
+        <v>-29.42606975469062</v>
       </c>
       <c r="F44">
-        <v>0.02409126192811027</v>
+        <v>-1.78551874785755</v>
       </c>
       <c r="G44">
-        <v>-5.266230273487693</v>
+        <v>-9.703047115132211</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.953688363831035</v>
       </c>
       <c r="E45">
-        <v>-23.15578387629867</v>
+        <v>-29.15810456001268</v>
       </c>
       <c r="F45">
-        <v>-0.6094283887522984</v>
+        <v>-1.49291453016668</v>
       </c>
       <c r="G45">
-        <v>-5.376669991180967</v>
+        <v>-9.379535393752112</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.655692315929995</v>
       </c>
       <c r="E46">
-        <v>-19.30059868971718</v>
+        <v>-28.55277193281326</v>
       </c>
       <c r="F46">
-        <v>0.08621633203586479</v>
+        <v>-1.610746479745299</v>
       </c>
       <c r="G46">
-        <v>-5.737153772088116</v>
+        <v>-9.620832157213462</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.353527001244292</v>
       </c>
       <c r="E47">
-        <v>-21.1991312633681</v>
+        <v>-28.47303235198221</v>
       </c>
       <c r="F47">
-        <v>-0.814739249536156</v>
+        <v>-1.743116277243049</v>
       </c>
       <c r="G47">
-        <v>-5.810181519790737</v>
+        <v>-9.655983222388212</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.060930744250238</v>
       </c>
       <c r="E48">
-        <v>-20.89056842798997</v>
+        <v>-28.168412990757</v>
       </c>
       <c r="F48">
-        <v>-0.5781691164402563</v>
+        <v>-1.587109844273818</v>
       </c>
       <c r="G48">
-        <v>-6.575252389982712</v>
+        <v>-9.336305379440162</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.786630367382787</v>
       </c>
       <c r="E49">
-        <v>-20.93109131088632</v>
+        <v>-26.97204101313255</v>
       </c>
       <c r="F49">
-        <v>-0.4564753180297865</v>
+        <v>-1.85070794898826</v>
       </c>
       <c r="G49">
-        <v>-5.912856883070041</v>
+        <v>-9.860112120478178</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.54766246200521</v>
       </c>
       <c r="E50">
-        <v>-21.37154767830704</v>
+        <v>-27.23366010090615</v>
       </c>
       <c r="F50">
-        <v>-0.5868197572276915</v>
+        <v>-1.86397011110708</v>
       </c>
       <c r="G50">
-        <v>-6.656522258359478</v>
+        <v>-9.287804271798755</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.349778680646246</v>
       </c>
       <c r="E51">
-        <v>-20.7233144547278</v>
+        <v>-26.55936547626361</v>
       </c>
       <c r="F51">
-        <v>-0.6862511816879245</v>
+        <v>-1.813224324011582</v>
       </c>
       <c r="G51">
-        <v>-6.58326737587743</v>
+        <v>-9.505733565797346</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.205186372584845</v>
       </c>
       <c r="E52">
-        <v>-20.6353951241925</v>
+        <v>-26.23283169548294</v>
       </c>
       <c r="F52">
-        <v>-1.25083161200515</v>
+        <v>-1.772529946981654</v>
       </c>
       <c r="G52">
-        <v>-6.589590599277106</v>
+        <v>-9.767528590415822</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.117673216808724</v>
       </c>
       <c r="E53">
-        <v>-17.80820034509859</v>
+        <v>-25.98740182545352</v>
       </c>
       <c r="F53">
-        <v>-0.8253522927008232</v>
+        <v>-1.964369897061185</v>
       </c>
       <c r="G53">
-        <v>-7.226823749820628</v>
+        <v>-9.904035287479067</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.089534548994874</v>
       </c>
       <c r="E54">
-        <v>-20.01936174801466</v>
+        <v>-25.9056666265809</v>
       </c>
       <c r="F54">
-        <v>-0.6629931101195229</v>
+        <v>-1.722956299761117</v>
       </c>
       <c r="G54">
-        <v>-7.381123976644606</v>
+        <v>-9.737655145432008</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.123104558968576</v>
       </c>
       <c r="E55">
-        <v>-19.55533590632554</v>
+        <v>-24.76440153341994</v>
       </c>
       <c r="F55">
-        <v>-1.015293624693139</v>
+        <v>-1.846679598308446</v>
       </c>
       <c r="G55">
-        <v>-6.306066347426794</v>
+        <v>-9.775339938232433</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.210772795382209</v>
       </c>
       <c r="E56">
-        <v>-18.48248666331848</v>
+        <v>-24.88435458290364</v>
       </c>
       <c r="F56">
-        <v>-0.6329117762542616</v>
+        <v>-2.178351279450145</v>
       </c>
       <c r="G56">
-        <v>-5.838615139132552</v>
+        <v>-9.873011809502868</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.351249826446472</v>
       </c>
       <c r="E57">
-        <v>-18.97248668863308</v>
+        <v>-24.70135163229772</v>
       </c>
       <c r="F57">
-        <v>-1.166721671027097</v>
+        <v>-2.050228521626548</v>
       </c>
       <c r="G57">
-        <v>-7.574277304473531</v>
+        <v>-10.0519156933535</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.531839269344927</v>
       </c>
       <c r="E58">
-        <v>-19.55454679617382</v>
+        <v>-24.42821568952037</v>
       </c>
       <c r="F58">
-        <v>-0.942178604252443</v>
+        <v>-2.166422788849832</v>
       </c>
       <c r="G58">
-        <v>-6.515150438750693</v>
+        <v>-10.00443669221951</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.746844032579301</v>
       </c>
       <c r="E59">
-        <v>-18.26722987356394</v>
+        <v>-23.85862767558809</v>
       </c>
       <c r="F59">
-        <v>-0.7151504352693909</v>
+        <v>-2.101737235100025</v>
       </c>
       <c r="G59">
-        <v>-6.912565812643731</v>
+        <v>-10.06189134843614</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.986433155328222</v>
       </c>
       <c r="E60">
-        <v>-19.29875881710028</v>
+        <v>-24.27563501186882</v>
       </c>
       <c r="F60">
-        <v>-1.393736586131704</v>
+        <v>-2.156166772035772</v>
       </c>
       <c r="G60">
-        <v>-7.222328047634731</v>
+        <v>-10.68228911248387</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.239859085440447</v>
       </c>
       <c r="E61">
-        <v>-16.75055600875173</v>
+        <v>-23.1980428015288</v>
       </c>
       <c r="F61">
-        <v>-1.320657185489329</v>
+        <v>-2.063084783717997</v>
       </c>
       <c r="G61">
-        <v>-6.640776857730473</v>
+        <v>-10.58328315072738</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.502538196757299</v>
       </c>
       <c r="E62">
-        <v>-18.69666777133989</v>
+        <v>-22.87703279181016</v>
       </c>
       <c r="F62">
-        <v>-0.9599769062689932</v>
+        <v>-2.299560482929977</v>
       </c>
       <c r="G62">
-        <v>-5.987581614756885</v>
+        <v>-10.8466211253992</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.762298814541599</v>
       </c>
       <c r="E63">
-        <v>-17.86078830689357</v>
+        <v>-23.04703619096937</v>
       </c>
       <c r="F63">
-        <v>-1.105858204473806</v>
+        <v>-2.314590381086372</v>
       </c>
       <c r="G63">
-        <v>-7.293027011162079</v>
+        <v>-10.8052277699071</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.016840054798083</v>
       </c>
       <c r="E64">
-        <v>-15.63259873754571</v>
+        <v>-23.14670910955392</v>
       </c>
       <c r="F64">
-        <v>-1.326481436698412</v>
+        <v>-2.517558618855112</v>
       </c>
       <c r="G64">
-        <v>-7.286998801901198</v>
+        <v>-11.09370982573593</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.257195985832091</v>
       </c>
       <c r="E65">
-        <v>-16.4550259505109</v>
+        <v>-23.01210768372756</v>
       </c>
       <c r="F65">
-        <v>-1.378761360223894</v>
+        <v>-2.495104892034829</v>
       </c>
       <c r="G65">
-        <v>-6.596488186486828</v>
+        <v>-10.94438567810262</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.479452575111718</v>
       </c>
       <c r="E66">
-        <v>-16.81493909070922</v>
+        <v>-23.0812171201727</v>
       </c>
       <c r="F66">
-        <v>-1.272707138378279</v>
+        <v>-2.516543868786683</v>
       </c>
       <c r="G66">
-        <v>-7.108914691852179</v>
+        <v>-11.00373051340321</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.680585100316879</v>
       </c>
       <c r="E67">
-        <v>-16.52212107946351</v>
+        <v>-23.05444551997286</v>
       </c>
       <c r="F67">
-        <v>-1.527538630868894</v>
+        <v>-2.629963933577991</v>
       </c>
       <c r="G67">
-        <v>-7.812549520326076</v>
+        <v>-11.34499399263059</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.853407355791114</v>
       </c>
       <c r="E68">
-        <v>-17.74778773316763</v>
+        <v>-22.8510959870866</v>
       </c>
       <c r="F68">
-        <v>-2.174077732019103</v>
+        <v>-2.696931639522512</v>
       </c>
       <c r="G68">
-        <v>-7.095046416584185</v>
+        <v>-11.26018395458827</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.999244183821466</v>
       </c>
       <c r="E69">
-        <v>-16.61516962598497</v>
+        <v>-22.05570202663472</v>
       </c>
       <c r="F69">
-        <v>-2.002857503330056</v>
+        <v>-2.729866699090417</v>
       </c>
       <c r="G69">
-        <v>-6.879798357280668</v>
+        <v>-10.92073624822402</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.111182969136285</v>
       </c>
       <c r="E70">
-        <v>-14.91555095552538</v>
+        <v>-22.23259145017049</v>
       </c>
       <c r="F70">
-        <v>-1.451490361454886</v>
+        <v>-2.660746894633423</v>
       </c>
       <c r="G70">
-        <v>-6.908829837133847</v>
+        <v>-10.80075164830563</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.191139375253234</v>
       </c>
       <c r="E71">
-        <v>-15.63705928650857</v>
+        <v>-22.49752895379262</v>
       </c>
       <c r="F71">
-        <v>-1.879557500525558</v>
+        <v>-2.748265567473997</v>
       </c>
       <c r="G71">
-        <v>-7.009763833770879</v>
+        <v>-10.93982731804653</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.238967642203823</v>
       </c>
       <c r="E72">
-        <v>-15.33862613355169</v>
+        <v>-22.46736833315172</v>
       </c>
       <c r="F72">
-        <v>-2.416706544299078</v>
+        <v>-3.05308571925395</v>
       </c>
       <c r="G72">
-        <v>-6.772543747988552</v>
+        <v>-11.23111722968311</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.253023099132642</v>
       </c>
       <c r="E73">
-        <v>-16.7997300308377</v>
+        <v>-22.67774094638826</v>
       </c>
       <c r="F73">
-        <v>-1.37928985862688</v>
+        <v>-2.72780820609446</v>
       </c>
       <c r="G73">
-        <v>-6.705353625191661</v>
+        <v>-10.62962908870882</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.239272869346978</v>
       </c>
       <c r="E74">
-        <v>-15.13475744924983</v>
+        <v>-23.06469149231121</v>
       </c>
       <c r="F74">
-        <v>-2.751588977494028</v>
+        <v>-3.009927777568096</v>
       </c>
       <c r="G74">
-        <v>-7.024078546363953</v>
+        <v>-10.6989965724947</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.195218087069786</v>
       </c>
       <c r="E75">
-        <v>-16.19428734353817</v>
+        <v>-22.93560968433554</v>
       </c>
       <c r="F75">
-        <v>-2.599992772577302</v>
+        <v>-2.991395542032666</v>
       </c>
       <c r="G75">
-        <v>-6.574041004492436</v>
+        <v>-10.48374590244659</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.128410263587011</v>
       </c>
       <c r="E76">
-        <v>-15.57777634805797</v>
+        <v>-23.35780022834966</v>
       </c>
       <c r="F76">
-        <v>-2.449813075919363</v>
+        <v>-3.125431186377445</v>
       </c>
       <c r="G76">
-        <v>-6.066653236187933</v>
+        <v>-10.25844647646729</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.041287782895902</v>
       </c>
       <c r="E77">
-        <v>-16.84723030875976</v>
+        <v>-23.89125530375594</v>
       </c>
       <c r="F77">
-        <v>-2.621903090381349</v>
+        <v>-3.306793117178966</v>
       </c>
       <c r="G77">
-        <v>-6.083072208921444</v>
+        <v>-10.20156879480529</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.938596928259306</v>
       </c>
       <c r="E78">
-        <v>-18.37077358510324</v>
+        <v>-23.31915875018345</v>
       </c>
       <c r="F78">
-        <v>-2.028416779543435</v>
+        <v>-3.123169743367803</v>
       </c>
       <c r="G78">
-        <v>-6.260401813783632</v>
+        <v>-10.02070946325592</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.830771784483973</v>
       </c>
       <c r="E79">
-        <v>-18.38320829980978</v>
+        <v>-23.74820209288354</v>
       </c>
       <c r="F79">
-        <v>-2.402433773948842</v>
+        <v>-3.168189026607747</v>
       </c>
       <c r="G79">
-        <v>-5.08755352441649</v>
+        <v>-9.778043364256531</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.719609612744212</v>
       </c>
       <c r="E80">
-        <v>-18.78078691351296</v>
+        <v>-24.61845768746547</v>
       </c>
       <c r="F80">
-        <v>-2.32169445993278</v>
+        <v>-3.275643189364093</v>
       </c>
       <c r="G80">
-        <v>-4.194517008091098</v>
+        <v>-9.630147293914554</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.618717707759786</v>
       </c>
       <c r="E81">
-        <v>-18.63137098289093</v>
+        <v>-24.64073551301184</v>
       </c>
       <c r="F81">
-        <v>-2.632501222932766</v>
+        <v>-3.470293790041324</v>
       </c>
       <c r="G81">
-        <v>-5.461015316686064</v>
+        <v>-9.342448461463052</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.530565314861169</v>
       </c>
       <c r="E82">
-        <v>-19.01475392028586</v>
+        <v>-25.17184817723092</v>
       </c>
       <c r="F82">
-        <v>-1.969543879859071</v>
+        <v>-3.384685332431606</v>
       </c>
       <c r="G82">
-        <v>-4.720065115771384</v>
+        <v>-9.318267745060162</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.466813104485515</v>
       </c>
       <c r="E83">
-        <v>-21.40405486334647</v>
+        <v>-26.11616383615718</v>
       </c>
       <c r="F83">
-        <v>-2.326161016968675</v>
+        <v>-3.465532334210033</v>
       </c>
       <c r="G83">
-        <v>-4.535200902019244</v>
+        <v>-9.010693314036514</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.436390471652178</v>
       </c>
       <c r="E84">
-        <v>-19.9771485081091</v>
+        <v>-26.97547571889818</v>
       </c>
       <c r="F84">
-        <v>-2.933206045455611</v>
+        <v>-3.527103226525314</v>
       </c>
       <c r="G84">
-        <v>-4.963939989516459</v>
+        <v>-9.002720100055255</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.442211257268704</v>
       </c>
       <c r="E85">
-        <v>-22.0947256002428</v>
+        <v>-27.49859760452829</v>
       </c>
       <c r="F85">
-        <v>-2.318052956830074</v>
+        <v>-3.469313831403813</v>
       </c>
       <c r="G85">
-        <v>-4.22217001480017</v>
+        <v>-9.114956010027214</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.496542096544603</v>
       </c>
       <c r="E86">
-        <v>-21.98349429454125</v>
+        <v>-28.29235519971819</v>
       </c>
       <c r="F86">
-        <v>-2.96751205307515</v>
+        <v>-3.367789950884108</v>
       </c>
       <c r="G86">
-        <v>-4.424659365286916</v>
+        <v>-9.059663050332025</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.595323557964144</v>
       </c>
       <c r="E87">
-        <v>-24.13105341922889</v>
+        <v>-29.4120152875674</v>
       </c>
       <c r="F87">
-        <v>-2.967132660804668</v>
+        <v>-3.540584077638473</v>
       </c>
       <c r="G87">
-        <v>-4.278431560738661</v>
+        <v>-8.482631059314985</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.746975889165144</v>
       </c>
       <c r="E88">
-        <v>-27.10938771164463</v>
+        <v>-29.41941008033125</v>
       </c>
       <c r="F88">
-        <v>-3.309994757190786</v>
+        <v>-3.578302958957546</v>
       </c>
       <c r="G88">
-        <v>-4.370408092683582</v>
+        <v>-8.672988279686829</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.947471960520986</v>
       </c>
       <c r="E89">
-        <v>-27.91148080196347</v>
+        <v>-31.40054795062735</v>
       </c>
       <c r="F89">
-        <v>-2.916886379253059</v>
+        <v>-3.79819474276548</v>
       </c>
       <c r="G89">
-        <v>-4.219021456823287</v>
+        <v>-8.646507497299167</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.196225529433577</v>
       </c>
       <c r="E90">
-        <v>-27.41193254381309</v>
+        <v>-32.51303336591291</v>
       </c>
       <c r="F90">
-        <v>-3.197331820205637</v>
+        <v>-3.66833986870263</v>
       </c>
       <c r="G90">
-        <v>-4.62085682130908</v>
+        <v>-8.617196667774737</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.497484361709936</v>
       </c>
       <c r="E91">
-        <v>-29.64102751322977</v>
+        <v>-33.89504765994021</v>
       </c>
       <c r="F91">
-        <v>-3.372413897726535</v>
+        <v>-3.812508931485856</v>
       </c>
       <c r="G91">
-        <v>-4.66494446521921</v>
+        <v>-8.95966500563091</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.843674306139017</v>
       </c>
       <c r="E92">
-        <v>-30.08703880079744</v>
+        <v>-35.15615989569609</v>
       </c>
       <c r="F92">
-        <v>-2.315214970108082</v>
+        <v>-4.026240146919171</v>
       </c>
       <c r="G92">
-        <v>-5.309850594116014</v>
+        <v>-8.58452450458925</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.245191510344322</v>
       </c>
       <c r="E93">
-        <v>-31.99173266344875</v>
+        <v>-36.18258661911987</v>
       </c>
       <c r="F93">
-        <v>-2.792834218846818</v>
+        <v>-3.923240115687677</v>
       </c>
       <c r="G93">
-        <v>-4.515035510797485</v>
+        <v>-9.120556057175152</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.691779574675754</v>
       </c>
       <c r="E94">
-        <v>-33.07845363228073</v>
+        <v>-37.18297686074831</v>
       </c>
       <c r="F94">
-        <v>-3.228066735951707</v>
+        <v>-3.994258538231887</v>
       </c>
       <c r="G94">
-        <v>-5.743484827721566</v>
+        <v>-9.118308206082204</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.188567311514861</v>
       </c>
       <c r="E95">
-        <v>-35.89092527722813</v>
+        <v>-39.19718882942968</v>
       </c>
       <c r="F95">
-        <v>-2.606829288752607</v>
+        <v>-4.046549230533606</v>
       </c>
       <c r="G95">
-        <v>-5.622468983689692</v>
+        <v>-8.782020806045493</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.735839944269611</v>
       </c>
       <c r="E96">
-        <v>-36.14425870840869</v>
+        <v>-41.17149466709644</v>
       </c>
       <c r="F96">
-        <v>-3.270860195980329</v>
+        <v>-4.24038720278869</v>
       </c>
       <c r="G96">
-        <v>-5.641313338148348</v>
+        <v>-9.17278791883726</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.31743052780835</v>
       </c>
       <c r="E97">
-        <v>-41.07554302585893</v>
+        <v>-42.95058503625662</v>
       </c>
       <c r="F97">
-        <v>-3.037046041233543</v>
+        <v>-4.227770338876651</v>
       </c>
       <c r="G97">
-        <v>-5.888704884857652</v>
+        <v>-9.123880840411935</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.946832576441457</v>
       </c>
       <c r="E98">
-        <v>-41.47834014959176</v>
+        <v>-44.336135789727</v>
       </c>
       <c r="F98">
-        <v>-2.753612679059068</v>
+        <v>-4.417342219007318</v>
       </c>
       <c r="G98">
-        <v>-6.304110899728051</v>
+        <v>-9.69916363255293</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.584502854068514</v>
       </c>
       <c r="E99">
-        <v>-43.351650270867</v>
+        <v>-45.63214123042842</v>
       </c>
       <c r="F99">
-        <v>-3.666240785703936</v>
+        <v>-4.437202327489436</v>
       </c>
       <c r="G99">
-        <v>-7.443264919402284</v>
+        <v>-9.81548274706539</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.25779287269112</v>
       </c>
       <c r="E100">
-        <v>-45.82400505739587</v>
+        <v>-47.50400395755696</v>
       </c>
       <c r="F100">
-        <v>-3.23083431144446</v>
+        <v>-4.485398399719116</v>
       </c>
       <c r="G100">
-        <v>-6.485215641268988</v>
+        <v>-9.994160801508889</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.89809776125209</v>
       </c>
       <c r="E101">
-        <v>-45.79990708698638</v>
+        <v>-49.52163817236999</v>
       </c>
       <c r="F101">
-        <v>-3.748141470818723</v>
+        <v>-4.610215971605544</v>
       </c>
       <c r="G101">
-        <v>-7.101588942529515</v>
+        <v>-10.53892137863518</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.57030996471688</v>
       </c>
       <c r="E102">
-        <v>-48.42476052524314</v>
+        <v>-51.21595942178476</v>
       </c>
       <c r="F102">
-        <v>-3.879017721889225</v>
+        <v>-4.564125609313779</v>
       </c>
       <c r="G102">
-        <v>-7.535011705823187</v>
+        <v>-10.82526523464389</v>
       </c>
     </row>
   </sheetData>
